--- a/SRC/Result/sonuc_birlesik_AUClideri_vs_nihai.xlsx
+++ b/SRC/Result/sonuc_birlesik_AUClideri_vs_nihai.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,70 +476,60 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>AUClideri_kaynak</t>
+          <t>Nihai_model</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Nihai_model</t>
+          <t>Nihai_aug</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Nihai_aug</t>
+          <t>Nihai_ablasyon</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Nihai_ablasyon</t>
+          <t>Nihai_esik</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Nihai_esik</t>
+          <t>Nihai_F1</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Nihai_F1</t>
+          <t>Nihai_MCC</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Nihai_MCC</t>
+          <t>Nihai_recall</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Nihai_macroF1</t>
+          <t>Nihai_precision</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Nihai_recall</t>
+          <t>Nihai_test_ROC_AUC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Nihai_precision</t>
+          <t>Nihai_cv_auc</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Nihai_test_ROC_AUC</t>
+          <t>ayni_mi</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Nihai_cv_auc</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>ayni_mi</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>not</t>
         </is>
@@ -583,56 +573,48 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>runs/ (matris first_pass)</t>
+          <t>Extra Trees</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>transfer_learning</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>clustering</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>feature_subsample</t>
-        </is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0.76</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9</v>
+        <v>0.846</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>0.612</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.76</v>
+        <v>0.733</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.9256</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.994</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>AYNI</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Saf cv_auc lideri = nihai (CatBoost/clustering 0.994). RF/original F1 0.880 daha yuksekti ama cv_auc dusuk (0.916); AUC-tutarlilik icin CatBoost secildi.</t>
+        <v>0.977</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>FARKLI (bilincli)</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>cv_auc tek-lideri CatBoost (0.994) iyimser (homojen kucuk panel). Nihai=ExtraTrees/transfer: cv_auc 0.977 marj-ici AMA testte lider (auc 0.979, F1 0.846, MCC 0.683, precision 0.733 -&gt; daha az yanli). Bilincli, kanit-temelli sapma.</t>
         </is>
       </c>
     </row>
@@ -674,56 +656,48 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>runs/ (matris first_pass)</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>clustering</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>clustering</t>
+          <t>smote</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>smote</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
           <t>0.80</t>
         </is>
       </c>
+      <c r="N3" t="n">
+        <v>0.722</v>
+      </c>
       <c r="O3" t="n">
-        <v>0.722</v>
+        <v>0.653</v>
       </c>
       <c r="P3" t="n">
-        <v>0.653</v>
+        <v>0.867</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.619</v>
       </c>
       <c r="R3" t="n">
-        <v>0.867</v>
+        <v>0.946</v>
       </c>
       <c r="S3" t="n">
-        <v>0.619</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.946</v>
-      </c>
-      <c r="U3" t="n">
         <v>0.904</v>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>AYNI</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Ayni model (CatBoost/clustering); nihai ablasyon=smote, esik 0.80.</t>
         </is>
@@ -767,56 +741,48 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>runs/ (matris first_pass)</t>
+          <t>Extra Trees</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Extra Trees</t>
+          <t>clustering</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>clustering</t>
+          <t>class_weight</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>class_weight</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
           <t>0.62 (dusuk, prior-OFF)</t>
         </is>
       </c>
+      <c r="N4" t="n">
+        <v>0.485</v>
+      </c>
       <c r="O4" t="n">
-        <v>0.485</v>
+        <v>0.38</v>
       </c>
       <c r="P4" t="n">
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.553</v>
+        <v>0.32</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0.786</v>
       </c>
       <c r="S4" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.786</v>
-      </c>
-      <c r="U4" t="n">
         <v>0.839</v>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>AYNI</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Ayni model (Extra Trees/clustering); nihai sadece esik 0.85-&gt;0.62 (prior-OFF).</t>
         </is>
@@ -860,56 +826,48 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>runs/ (matris first_pass)</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>original + capraz-panel benign + uzman-stacking</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>original + capraz-panel benign + uzman-stacking</t>
+          <t>class_weight</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>class_weight</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
           <t>0.65 (F1-optimize)</t>
         </is>
       </c>
+      <c r="N5" t="n">
+        <v>0.582</v>
+      </c>
       <c r="O5" t="n">
-        <v>0.582</v>
+        <v>0.467</v>
       </c>
       <c r="P5" t="n">
-        <v>0.467</v>
+        <v>0.745</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.719</v>
+        <v>0.477</v>
       </c>
       <c r="R5" t="n">
-        <v>0.745</v>
+        <v>0.853</v>
       </c>
       <c r="S5" t="n">
-        <v>0.477</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.853</v>
-      </c>
-      <c r="U5" t="n">
         <v>0.854</v>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>AYNI</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Ayni taban (CatBoost/original); nihai +capraz-panel benign +uzman-stacking +F1-esik 0.65.</t>
         </is>
